--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5633,10 +5633,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134665086</v>
+        <v>135287667</v>
       </c>
       <c r="B48" t="n">
-        <v>99142</v>
+        <v>57153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5644,37 +5644,47 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6010639</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blodnycklar × fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta × maculata</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Olshammar, Nrk</t>
+          <t>Bergsjön, Bergsjön, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483472</v>
+        <v>475000</v>
       </c>
       <c r="R48" t="n">
-        <v>6512384</v>
+        <v>6512402</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5683,42 +5693,27 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Laxå</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Västergötland</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Tived</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5733,64 +5728,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>92087603</v>
+        <v>134665086</v>
       </c>
       <c r="B49" t="n">
-        <v>56522</v>
+        <v>99142</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>206004</v>
+        <v>6010639</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blodnycklar × fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. cruenta × maculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tiveden, Vg</t>
+          <t>Olshammar, Nrk</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476171</v>
+        <v>483472</v>
       </c>
       <c r="R49" t="n">
-        <v>6510583</v>
+        <v>6512384</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5799,37 +5790,42 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Laxå</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Västergötland</t>
+          <t>Närke</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Tived</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5844,15 +5840,126 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>92087603</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tiveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>476171</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6510583</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
           <t>David van der Spoel</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>David van der Spoel</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93066368</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134756580</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134081371</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133128591</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132852808</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104756046</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125365912</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132716740</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1697,6 +1742,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132716894</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1814,6 +1864,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717140</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1926,6 +1981,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717255</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2033,6 +2093,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717308</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2140,6 +2205,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717342</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2247,6 +2317,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717397</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2354,6 +2429,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717687</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2461,6 +2541,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132717771</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2568,6 +2653,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718144</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2675,6 +2765,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718170</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2782,6 +2877,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718216</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2889,6 +2989,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718239</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2996,6 +3101,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718272</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3103,6 +3213,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718322</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3210,6 +3325,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718362</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3317,6 +3437,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718412</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3424,6 +3549,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718438</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3531,6 +3661,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718497</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3638,6 +3773,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718639</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3745,6 +3885,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718683</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3852,6 +3997,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718708</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3959,6 +4109,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718743</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4066,6 +4221,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718798</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4173,6 +4333,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718831</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4280,6 +4445,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718843</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4387,6 +4557,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718894</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4494,6 +4669,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718905</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4601,6 +4781,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132718924</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4701,6 +4886,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61959662</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4801,6 +4991,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61959658</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4902,6 +5097,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75198507</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5014,6 +5214,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61715145</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5118,6 +5323,11 @@
       <c r="AY42" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107476655</t>
         </is>
       </c>
     </row>
@@ -5216,6 +5426,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61956895</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5324,6 +5539,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61715134</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5432,6 +5652,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61715139</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5531,6 +5756,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61715117</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5630,6 +5860,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61715121</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5737,6 +5972,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135287667</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5849,6 +6089,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665086</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5960,8 +6205,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92087603</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -5871,7 +5871,7 @@
         <v>135287667</v>
       </c>
       <c r="B48" t="n">
-        <v>57153</v>
+        <v>57158</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ49"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5868,10 +5868,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134665086</v>
+        <v>135287667</v>
       </c>
       <c r="B48" t="n">
-        <v>99142</v>
+        <v>57158</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5879,37 +5879,47 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6010639</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blodnycklar × fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta × maculata</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Olshammar, Nrk</t>
+          <t>Bergsjön, Bergsjön, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483472</v>
+        <v>475000</v>
       </c>
       <c r="R48" t="n">
-        <v>6512384</v>
+        <v>6512402</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5918,42 +5928,27 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Laxå</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Västergötland</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Tived</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5968,69 +5963,65 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665086</t>
+          <t>https://artportalen.se/Sighting/135287667</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>92087603</v>
+        <v>134665086</v>
       </c>
       <c r="B49" t="n">
-        <v>56522</v>
+        <v>99142</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>206004</v>
+        <v>6010639</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Blodnycklar × fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. cruenta × maculata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Tiveden, Vg</t>
+          <t>Olshammar, Nrk</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476171</v>
+        <v>483472</v>
       </c>
       <c r="R49" t="n">
-        <v>6510583</v>
+        <v>6512384</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6039,37 +6030,42 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Laxå</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Västergötland</t>
+          <t>Närke</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Tived</t>
+          <t>Askersund</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6084,16 +6080,132 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>David van der Spoel</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>David van der Spoel</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665086</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>92087603</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tiveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>476171</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6510583</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/92087603</t>
         </is>
@@ -6149,6 +6261,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ50"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5980,10 +5980,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134665086</v>
+        <v>136307649</v>
       </c>
       <c r="B49" t="n">
-        <v>99142</v>
+        <v>57165</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5991,37 +5991,47 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6010639</v>
+        <v>102612</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blodnycklar × fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta × maculata</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Olshammar, Nrk</t>
+          <t>Bergsjön, Bergsjön, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483472</v>
+        <v>475015</v>
       </c>
       <c r="R49" t="n">
-        <v>6512384</v>
+        <v>6512380</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6030,42 +6040,37 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Laxå</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Närke</t>
+          <t>Västergötland</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Askersund</t>
+          <t>Tived</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6080,27 +6085,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134665086</t>
+          <t>https://artportalen.se/Sighting/136307649</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>92087603</v>
+        <v>136307714</v>
       </c>
       <c r="B50" t="n">
-        <v>56522</v>
+        <v>58148</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6108,41 +6113,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tiveden, Vg</t>
+          <t>Bergsjön, Bergsjön, Vg</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476171</v>
+        <v>475023</v>
       </c>
       <c r="R50" t="n">
-        <v>6510583</v>
+        <v>6512397</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6166,22 +6172,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>05:38</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6196,16 +6202,249 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>David van der Spoel</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>David van der Spoel</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136307714</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134665086</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6010639</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blodnycklar × fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. cruenta × maculata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Olshammar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>483472</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6512384</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134665086</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>92087603</v>
+      </c>
+      <c r="B52" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Tiveden, Vg</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>476171</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6510583</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Tived</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>05:38</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/92087603</t>
         </is>
@@ -6262,6 +6501,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3853-2024 artfynd.xlsx
+++ b/artfynd/S 3853-2024 artfynd.xlsx
@@ -5983,7 +5983,7 @@
         <v>136307649</v>
       </c>
       <c r="B49" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>136307714</v>
       </c>
       <c r="B50" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
